--- a/site/audit-page/verdict-mix.xlsx
+++ b/site/audit-page/verdict-mix.xlsx
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="C7">
-        <f>BAHTTEXT(A1)</f>
+        <f>ODDLYIELD(A1,A2,A3,A4,A5,B1,B2)</f>
         <v/>
       </c>
     </row>

--- a/site/audit-page/verdict-mix.xlsx
+++ b/site/audit-page/verdict-mix.xlsx
@@ -485,7 +485,7 @@
     </row>
     <row r="7">
       <c r="C7">
-        <f>ODDLYIELD(A1,A2,A3,A4,A5,B1,B2)</f>
+        <f>WEBSERVICE("https://example.com/rates.xml")</f>
         <v/>
       </c>
     </row>
